--- a/Result/profitability/7777.xlsx
+++ b/Result/profitability/7777.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM11"/>
+  <dimension ref="A1:AM12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,7 +1329,7 @@
         <v>-135</v>
       </c>
       <c r="E8" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
@@ -1436,27 +1436,27 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D9" t="n">
         <v>39</v>
       </c>
       <c r="E9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F9" t="n">
-        <v>52.04</v>
+        <v>51.84</v>
       </c>
       <c r="G9" t="n">
         <v>32</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>39.43%</t>
+          <t>39.18%</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
         <v>34</v>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>-1.678576085539184</v>
+        <v>-1.675968183596297</v>
       </c>
       <c r="AA9" t="n">
         <v>-0.05000000000000002</v>
@@ -1512,10 +1512,10 @@
         <v>-0.1851851851851852</v>
       </c>
       <c r="AC9" t="n">
-        <v>-10.85</v>
+        <v>-11.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.1725234536492288</v>
+        <v>-0.1757036094768644</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1625,10 +1625,10 @@
         <v>0.09090909090909083</v>
       </c>
       <c r="Y10" t="n">
-        <v>47.96</v>
+        <v>48.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.9215987701767872</v>
+        <v>0.9290123456790123</v>
       </c>
       <c r="AA10" t="n">
         <v>0.09999999999999998</v>
@@ -1795,6 +1795,129 @@
       </c>
       <c r="AM11" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7777</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>170</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-46</v>
+      </c>
+      <c r="E12" t="n">
+        <v>216</v>
+      </c>
+      <c r="F12" t="n">
+        <v>127.22</v>
+      </c>
+      <c r="G12" t="n">
+        <v>202</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>118.94%</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>204</v>
+      </c>
+      <c r="K12" t="n">
+        <v>197</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>699.58</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-1.222272695506325</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.019230769230769</v>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>-2.658886425870387</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK12" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
